--- a/sov/proj_02/Data_02.xlsx
+++ b/sov/proj_02/Data_02.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Programming\R\sov\proj_02\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Programming\Py\sov\proj_02\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{668E19AE-F0AD-45BE-A5AF-42488CCBDA72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8878F08E-D15F-44CE-AC28-A614D85DB9AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="8415" yWindow="2550" windowWidth="28365" windowHeight="16305" xr2:uid="{DE67C0CD-2877-4965-A94D-22D205E78752}"/>
   </bookViews>
@@ -27,8 +27,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
